--- a/public/sample_shifts.xlsx
+++ b/public/sample_shifts.xlsx
@@ -3,7 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="ตารางเวร" sheetId="1" r:id="rId1"/>
+    <sheet name="เภสัช" sheetId="1" r:id="rId1"/>
+    <sheet name="จพง" sheetId="2" r:id="rId2"/>
+    <sheet name="จนท" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -397,133 +399,136 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AF4"/>
+  <dimension ref="A1:AG5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>phaID / Name</v>
+        <v>เภสัช</v>
       </c>
       <c r="B1" t="str">
+        <v>ชื่อ-นามสกุล</v>
+      </c>
+      <c r="C1" t="str">
         <v>1</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>2</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>3</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>4</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>5</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>6</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>7</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>8</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>9</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>10</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>11</v>
       </c>
-      <c r="M1" t="str">
+      <c r="N1" t="str">
         <v>12</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>13</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>14</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>15</v>
       </c>
-      <c r="Q1" t="str">
+      <c r="R1" t="str">
         <v>16</v>
       </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>17</v>
       </c>
-      <c r="S1" t="str">
+      <c r="T1" t="str">
         <v>18</v>
       </c>
-      <c r="T1" t="str">
+      <c r="U1" t="str">
         <v>19</v>
       </c>
-      <c r="U1" t="str">
+      <c r="V1" t="str">
         <v>20</v>
       </c>
-      <c r="V1" t="str">
+      <c r="W1" t="str">
         <v>21</v>
       </c>
-      <c r="W1" t="str">
+      <c r="X1" t="str">
         <v>22</v>
       </c>
-      <c r="X1" t="str">
+      <c r="Y1" t="str">
         <v>23</v>
       </c>
-      <c r="Y1" t="str">
+      <c r="Z1" t="str">
         <v>24</v>
       </c>
-      <c r="Z1" t="str">
+      <c r="AA1" t="str">
         <v>25</v>
       </c>
-      <c r="AA1" t="str">
+      <c r="AB1" t="str">
         <v>26</v>
       </c>
-      <c r="AB1" t="str">
+      <c r="AC1" t="str">
         <v>27</v>
       </c>
-      <c r="AC1" t="str">
+      <c r="AD1" t="str">
         <v>28</v>
       </c>
-      <c r="AD1" t="str">
+      <c r="AE1" t="str">
         <v>29</v>
       </c>
-      <c r="AE1" t="str">
+      <c r="AF1" t="str">
         <v>30</v>
       </c>
-      <c r="AF1" t="str">
+      <c r="AG1" t="str">
         <v>31</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>pha001</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>smc</v>
+        <v>สมชาย ใจดี</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>e</v>
       </c>
       <c r="D2" t="str">
-        <v>S</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>d</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>c</v>
       </c>
       <c r="G2" t="str">
-        <v>รO</v>
+        <v/>
       </c>
       <c r="H2" t="str">
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>บE</v>
+        <v/>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -532,7 +537,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>c</v>
+        <v/>
       </c>
       <c r="M2" t="str">
         <v/>
@@ -544,7 +549,7 @@
         <v/>
       </c>
       <c r="P2" t="str">
-        <v>d</v>
+        <v/>
       </c>
       <c r="Q2" t="str">
         <v/>
@@ -553,7 +558,7 @@
         <v/>
       </c>
       <c r="S2" t="str">
-        <v>ด</v>
+        <v/>
       </c>
       <c r="T2" t="str">
         <v/>
@@ -562,51 +567,72 @@
         <v/>
       </c>
       <c r="V2" t="str">
-        <v>chem</v>
+        <v/>
       </c>
       <c r="W2" t="str">
         <v/>
       </c>
       <c r="X2" t="str">
-        <v>Ext</v>
+        <v/>
       </c>
       <c r="Y2" t="str">
         <v/>
       </c>
       <c r="Z2" t="str">
-        <v>รH</v>
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v/>
+      </c>
+      <c r="AB2" t="str">
+        <v/>
+      </c>
+      <c r="AC2" t="str">
+        <v/>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>pha002</v>
+        <v/>
       </c>
       <c r="B3" t="str">
-        <v/>
+        <v>วิไล รักษา</v>
       </c>
       <c r="C3" t="str">
-        <v>บM</v>
+        <v/>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>บe</v>
       </c>
       <c r="E3" t="str">
-        <v>Ext</v>
+        <v>รo</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>ด</v>
       </c>
       <c r="G3" t="str">
         <v/>
       </c>
       <c r="H3" t="str">
-        <v>S</v>
+        <v/>
       </c>
       <c r="I3" t="str">
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>รE</v>
+        <v/>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -615,7 +641,7 @@
         <v/>
       </c>
       <c r="M3" t="str">
-        <v>smc</v>
+        <v/>
       </c>
       <c r="N3" t="str">
         <v/>
@@ -627,7 +653,7 @@
         <v/>
       </c>
       <c r="Q3" t="str">
-        <v>บE</v>
+        <v/>
       </c>
       <c r="R3" t="str">
         <v/>
@@ -636,7 +662,7 @@
         <v/>
       </c>
       <c r="T3" t="str">
-        <v>c</v>
+        <v/>
       </c>
       <c r="U3" t="str">
         <v/>
@@ -645,36 +671,57 @@
         <v/>
       </c>
       <c r="W3" t="str">
-        <v>d</v>
+        <v/>
       </c>
       <c r="X3" t="str">
         <v/>
       </c>
       <c r="Y3" t="str">
-        <v>ด</v>
+        <v/>
       </c>
       <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v/>
+      </c>
+      <c r="AB3" t="str">
+        <v/>
+      </c>
+      <c r="AC3" t="str">
+        <v/>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>พี่กุส</v>
+        <v/>
       </c>
       <c r="B4" t="str">
-        <v>S</v>
+        <v>มานี มีสุข</v>
       </c>
       <c r="C4" t="str">
-        <v/>
+        <v>s</v>
       </c>
       <c r="D4" t="str">
-        <v/>
+        <v>smc</v>
       </c>
       <c r="E4" t="str">
-        <v/>
+        <v>ch</v>
       </c>
       <c r="F4" t="str">
-        <v>smc</v>
+        <v>ext</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -686,7 +733,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>Ext</v>
+        <v/>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -698,7 +745,7 @@
         <v/>
       </c>
       <c r="N4" t="str">
-        <v>รO</v>
+        <v/>
       </c>
       <c r="O4" t="str">
         <v/>
@@ -710,7 +757,7 @@
         <v/>
       </c>
       <c r="R4" t="str">
-        <v>บM</v>
+        <v/>
       </c>
       <c r="S4" t="str">
         <v/>
@@ -722,7 +769,7 @@
         <v/>
       </c>
       <c r="V4" t="str">
-        <v>c</v>
+        <v/>
       </c>
       <c r="W4" t="str">
         <v/>
@@ -734,12 +781,1166 @@
         <v/>
       </c>
       <c r="Z4" t="str">
-        <v>d</v>
+        <v/>
+      </c>
+      <c r="AA4" t="str">
+        <v/>
+      </c>
+      <c r="AB4" t="str">
+        <v/>
+      </c>
+      <c r="AC4" t="str">
+        <v/>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
+        <v/>
+      </c>
+      <c r="AG4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v>พลอย งาม</v>
+      </c>
+      <c r="C5" t="str">
+        <v>บm</v>
+      </c>
+      <c r="D5" t="str">
+        <v>รe</v>
+      </c>
+      <c r="E5" t="str">
+        <v>รh</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
+        <v/>
+      </c>
+      <c r="AB5" t="str">
+        <v/>
+      </c>
+      <c r="AC5" t="str">
+        <v/>
+      </c>
+      <c r="AD5" t="str">
+        <v/>
+      </c>
+      <c r="AE5" t="str">
+        <v/>
+      </c>
+      <c r="AF5" t="str">
+        <v/>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AF4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AG5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AG5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>จพง</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ชื่อ-นามสกุล</v>
+      </c>
+      <c r="C1" t="str">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2</v>
+      </c>
+      <c r="E1" t="str">
+        <v>3</v>
+      </c>
+      <c r="F1" t="str">
+        <v>4</v>
+      </c>
+      <c r="G1" t="str">
+        <v>5</v>
+      </c>
+      <c r="H1" t="str">
+        <v>6</v>
+      </c>
+      <c r="I1" t="str">
+        <v>7</v>
+      </c>
+      <c r="J1" t="str">
+        <v>8</v>
+      </c>
+      <c r="K1" t="str">
+        <v>9</v>
+      </c>
+      <c r="L1" t="str">
+        <v>10</v>
+      </c>
+      <c r="M1" t="str">
+        <v>11</v>
+      </c>
+      <c r="N1" t="str">
+        <v>12</v>
+      </c>
+      <c r="O1" t="str">
+        <v>13</v>
+      </c>
+      <c r="P1" t="str">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>15</v>
+      </c>
+      <c r="R1" t="str">
+        <v>16</v>
+      </c>
+      <c r="S1" t="str">
+        <v>17</v>
+      </c>
+      <c r="T1" t="str">
+        <v>18</v>
+      </c>
+      <c r="U1" t="str">
+        <v>19</v>
+      </c>
+      <c r="V1" t="str">
+        <v>20</v>
+      </c>
+      <c r="W1" t="str">
+        <v>21</v>
+      </c>
+      <c r="X1" t="str">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>23</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>24</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v>สุดา เพชร</v>
+      </c>
+      <c r="C2" t="str">
+        <v>m1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>m2</v>
+      </c>
+      <c r="E2" t="str">
+        <v>m3</v>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v/>
+      </c>
+      <c r="AB2" t="str">
+        <v/>
+      </c>
+      <c r="AC2" t="str">
+        <v/>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v>บุญมี สว่าง</v>
+      </c>
+      <c r="C3" t="str">
+        <v>s1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>บe</v>
+      </c>
+      <c r="E3" t="str">
+        <v>รo</v>
+      </c>
+      <c r="F3" t="str">
+        <v>ด</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v/>
+      </c>
+      <c r="AB3" t="str">
+        <v/>
+      </c>
+      <c r="AC3" t="str">
+        <v/>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v>แก้ว แสง</v>
+      </c>
+      <c r="C4" t="str">
+        <v>smc1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>smc2</v>
+      </c>
+      <c r="E4" t="str">
+        <v>บm1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>e</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
+        <v/>
+      </c>
+      <c r="AB4" t="str">
+        <v/>
+      </c>
+      <c r="AC4" t="str">
+        <v/>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
+        <v/>
+      </c>
+      <c r="AG4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v>ทอง ดี</v>
+      </c>
+      <c r="C5" t="str">
+        <v>รe</v>
+      </c>
+      <c r="D5" t="str">
+        <v>รh</v>
+      </c>
+      <c r="E5" t="str">
+        <v>บm2</v>
+      </c>
+      <c r="F5" t="str">
+        <v>s2</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
+        <v/>
+      </c>
+      <c r="AB5" t="str">
+        <v/>
+      </c>
+      <c r="AC5" t="str">
+        <v/>
+      </c>
+      <c r="AD5" t="str">
+        <v/>
+      </c>
+      <c r="AE5" t="str">
+        <v/>
+      </c>
+      <c r="AF5" t="str">
+        <v/>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:AG5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AG5"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>จนท</v>
+      </c>
+      <c r="B1" t="str">
+        <v>ชื่อ-นามสกุล</v>
+      </c>
+      <c r="C1" t="str">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <v>2</v>
+      </c>
+      <c r="E1" t="str">
+        <v>3</v>
+      </c>
+      <c r="F1" t="str">
+        <v>4</v>
+      </c>
+      <c r="G1" t="str">
+        <v>5</v>
+      </c>
+      <c r="H1" t="str">
+        <v>6</v>
+      </c>
+      <c r="I1" t="str">
+        <v>7</v>
+      </c>
+      <c r="J1" t="str">
+        <v>8</v>
+      </c>
+      <c r="K1" t="str">
+        <v>9</v>
+      </c>
+      <c r="L1" t="str">
+        <v>10</v>
+      </c>
+      <c r="M1" t="str">
+        <v>11</v>
+      </c>
+      <c r="N1" t="str">
+        <v>12</v>
+      </c>
+      <c r="O1" t="str">
+        <v>13</v>
+      </c>
+      <c r="P1" t="str">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>15</v>
+      </c>
+      <c r="R1" t="str">
+        <v>16</v>
+      </c>
+      <c r="S1" t="str">
+        <v>17</v>
+      </c>
+      <c r="T1" t="str">
+        <v>18</v>
+      </c>
+      <c r="U1" t="str">
+        <v>19</v>
+      </c>
+      <c r="V1" t="str">
+        <v>20</v>
+      </c>
+      <c r="W1" t="str">
+        <v>21</v>
+      </c>
+      <c r="X1" t="str">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>23</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>24</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>25</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>26</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>27</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>28</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>29</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>30</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v/>
+      </c>
+      <c r="B2" t="str">
+        <v>เอก เก่ง</v>
+      </c>
+      <c r="C2" t="str">
+        <v>m1</v>
+      </c>
+      <c r="D2" t="str">
+        <v>m2</v>
+      </c>
+      <c r="E2" t="str">
+        <v>m3</v>
+      </c>
+      <c r="F2" t="str">
+        <v>m4</v>
+      </c>
+      <c r="G2" t="str">
+        <v/>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
+        <v/>
+      </c>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
+        <v/>
+      </c>
+      <c r="X2" t="str">
+        <v/>
+      </c>
+      <c r="Y2" t="str">
+        <v/>
+      </c>
+      <c r="Z2" t="str">
+        <v/>
+      </c>
+      <c r="AA2" t="str">
+        <v/>
+      </c>
+      <c r="AB2" t="str">
+        <v/>
+      </c>
+      <c r="AC2" t="str">
+        <v/>
+      </c>
+      <c r="AD2" t="str">
+        <v/>
+      </c>
+      <c r="AE2" t="str">
+        <v/>
+      </c>
+      <c r="AF2" t="str">
+        <v/>
+      </c>
+      <c r="AG2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v/>
+      </c>
+      <c r="B3" t="str">
+        <v>โอ๊ค ดี</v>
+      </c>
+      <c r="C3" t="str">
+        <v>s1</v>
+      </c>
+      <c r="D3" t="str">
+        <v>s2</v>
+      </c>
+      <c r="E3" t="str">
+        <v>s3</v>
+      </c>
+      <c r="F3" t="str">
+        <v>ext1</v>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
+        <v/>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v/>
+      </c>
+      <c r="S3" t="str">
+        <v/>
+      </c>
+      <c r="T3" t="str">
+        <v/>
+      </c>
+      <c r="U3" t="str">
+        <v/>
+      </c>
+      <c r="V3" t="str">
+        <v/>
+      </c>
+      <c r="W3" t="str">
+        <v/>
+      </c>
+      <c r="X3" t="str">
+        <v/>
+      </c>
+      <c r="Y3" t="str">
+        <v/>
+      </c>
+      <c r="Z3" t="str">
+        <v/>
+      </c>
+      <c r="AA3" t="str">
+        <v/>
+      </c>
+      <c r="AB3" t="str">
+        <v/>
+      </c>
+      <c r="AC3" t="str">
+        <v/>
+      </c>
+      <c r="AD3" t="str">
+        <v/>
+      </c>
+      <c r="AE3" t="str">
+        <v/>
+      </c>
+      <c r="AF3" t="str">
+        <v/>
+      </c>
+      <c r="AG3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v/>
+      </c>
+      <c r="B4" t="str">
+        <v>นาย ใจ</v>
+      </c>
+      <c r="C4" t="str">
+        <v>บe1</v>
+      </c>
+      <c r="D4" t="str">
+        <v>บe2</v>
+      </c>
+      <c r="E4" t="str">
+        <v>smc1</v>
+      </c>
+      <c r="F4" t="str">
+        <v>smc2</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
+        <v/>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v/>
+      </c>
+      <c r="S4" t="str">
+        <v/>
+      </c>
+      <c r="T4" t="str">
+        <v/>
+      </c>
+      <c r="U4" t="str">
+        <v/>
+      </c>
+      <c r="V4" t="str">
+        <v/>
+      </c>
+      <c r="W4" t="str">
+        <v/>
+      </c>
+      <c r="X4" t="str">
+        <v/>
+      </c>
+      <c r="Y4" t="str">
+        <v/>
+      </c>
+      <c r="Z4" t="str">
+        <v/>
+      </c>
+      <c r="AA4" t="str">
+        <v/>
+      </c>
+      <c r="AB4" t="str">
+        <v/>
+      </c>
+      <c r="AC4" t="str">
+        <v/>
+      </c>
+      <c r="AD4" t="str">
+        <v/>
+      </c>
+      <c r="AE4" t="str">
+        <v/>
+      </c>
+      <c r="AF4" t="str">
+        <v/>
+      </c>
+      <c r="AG4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v/>
+      </c>
+      <c r="B5" t="str">
+        <v>มาลี ศรี</v>
+      </c>
+      <c r="C5" t="str">
+        <v>รo1</v>
+      </c>
+      <c r="D5" t="str">
+        <v>รo2</v>
+      </c>
+      <c r="E5" t="str">
+        <v>รe</v>
+      </c>
+      <c r="F5" t="str">
+        <v>ด</v>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
+        <v/>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v/>
+      </c>
+      <c r="S5" t="str">
+        <v/>
+      </c>
+      <c r="T5" t="str">
+        <v/>
+      </c>
+      <c r="U5" t="str">
+        <v/>
+      </c>
+      <c r="V5" t="str">
+        <v/>
+      </c>
+      <c r="W5" t="str">
+        <v/>
+      </c>
+      <c r="X5" t="str">
+        <v/>
+      </c>
+      <c r="Y5" t="str">
+        <v/>
+      </c>
+      <c r="Z5" t="str">
+        <v/>
+      </c>
+      <c r="AA5" t="str">
+        <v/>
+      </c>
+      <c r="AB5" t="str">
+        <v/>
+      </c>
+      <c r="AC5" t="str">
+        <v/>
+      </c>
+      <c r="AD5" t="str">
+        <v/>
+      </c>
+      <c r="AE5" t="str">
+        <v/>
+      </c>
+      <c r="AF5" t="str">
+        <v/>
+      </c>
+      <c r="AG5" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:AG5"/>
   </ignoredErrors>
 </worksheet>
 </file>